--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/06_Rechnungen_und_Forderungen.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/06_Rechnungen_und_Forderungen.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Forderungen" sheetId="1" r:id="R5e677c4795ca4767"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abgrenzung" sheetId="2" r:id="R0a9d6345a1f64b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summen_Alter" sheetId="3" r:id="R22a8657d9ea64d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungen_nach_Eroeffnung" sheetId="4" r:id="R25e98de58fb349a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Forderungen" sheetId="1" r:id="R39bb7c9c0d404f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abgrenzung" sheetId="2" r:id="Rb30c7ff90fc141be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summen_Alter" sheetId="3" r:id="R4991817e493340ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungen_nach_Eroeffnung" sheetId="4" r:id="R7a55c33900984cfd"/>
   </x:sheets>
 </x:workbook>
 </file>
